--- a/PFP-C/Input data and Generated Schedule/161.xlsx
+++ b/PFP-C/Input data and Generated Schedule/161.xlsx
@@ -46226,7 +46226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46251,7 +46251,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -46261,7 +46261,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -46271,11 +46271,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>74.04349999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -68259,7 +68379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68295,25 +68415,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -68346,18 +68461,15 @@
         <v>7.658959537572244</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>291.3318318318318</v>
       </c>
       <c r="I2" t="n">
-        <v>291.3318318318318</v>
+        <v>3.978978978978974</v>
       </c>
       <c r="J2" t="n">
-        <v>3.978978978978974</v>
-      </c>
-      <c r="K2" t="n">
         <v>1.365789297365829</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68390,18 +68502,15 @@
         <v>7.832898172323742</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>325.5382882882883</v>
       </c>
       <c r="I3" t="n">
-        <v>325.5382882882883</v>
+        <v>4.504504504504495</v>
       </c>
       <c r="J3" t="n">
-        <v>4.504504504504495</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.383709587031871</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68434,18 +68543,15 @@
         <v>7.551622418879036</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>303.0487987987988</v>
       </c>
       <c r="I4" t="n">
-        <v>303.0487987987988</v>
+        <v>3.843843843843834</v>
       </c>
       <c r="J4" t="n">
-        <v>3.843843843843834</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.268391050906574</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68478,18 +68584,15 @@
         <v>7.885117493472574</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>339.6524024024024</v>
       </c>
       <c r="I5" t="n">
-        <v>339.6524024024024</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J5" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.335051512211078</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68522,18 +68625,15 @@
         <v>7.645739910313905</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>378.3438438438438</v>
       </c>
       <c r="I6" t="n">
-        <v>378.3438438438438</v>
+        <v>5.120120120120123</v>
       </c>
       <c r="J6" t="n">
-        <v>5.120120120120123</v>
-      </c>
-      <c r="K6" t="n">
         <v>1.353298118479068</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68566,18 +68666,15 @@
         <v>3.476821192052965</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>254.7282282282282</v>
       </c>
       <c r="I7" t="n">
-        <v>254.7282282282282</v>
+        <v>1.57657657657657</v>
       </c>
       <c r="J7" t="n">
-        <v>1.57657657657657</v>
-      </c>
-      <c r="K7" t="n">
         <v>0.6189249568226134</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68610,18 +68707,15 @@
         <v>6.758893280632421</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>225.9361861861862</v>
       </c>
       <c r="I8" t="n">
-        <v>225.9361861861862</v>
+        <v>2.567567567567571</v>
       </c>
       <c r="J8" t="n">
-        <v>2.567567567567571</v>
-      </c>
-      <c r="K8" t="n">
         <v>1.136412723835095</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68654,18 +68748,15 @@
         <v>7.916666666666679</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>205.5435435435435</v>
       </c>
       <c r="I9" t="n">
-        <v>205.5435435435435</v>
+        <v>2.567567567567571</v>
       </c>
       <c r="J9" t="n">
-        <v>2.567567567567571</v>
-      </c>
-      <c r="K9" t="n">
         <v>1.249159921690093</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68698,18 +68789,15 @@
         <v>8.53754940711463</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>227.1373873873875</v>
       </c>
       <c r="I10" t="n">
-        <v>227.1373873873875</v>
+        <v>3.243243243243246</v>
       </c>
       <c r="J10" t="n">
-        <v>3.243243243243246</v>
-      </c>
-      <c r="K10" t="n">
         <v>1.427877321540125</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68742,18 +68830,15 @@
         <v>7.196531791907517</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>287.1276276276276</v>
       </c>
       <c r="I11" t="n">
-        <v>287.1276276276276</v>
+        <v>3.73873873873874</v>
       </c>
       <c r="J11" t="n">
-        <v>3.73873873873874</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.302117378822029</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68786,18 +68871,15 @@
         <v>8.737201365187705</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>269.1493993993994</v>
       </c>
       <c r="I12" t="n">
-        <v>269.1493993993994</v>
+        <v>3.84384384384384</v>
       </c>
       <c r="J12" t="n">
-        <v>3.84384384384384</v>
-      </c>
-      <c r="K12" t="n">
         <v>1.428145057139748</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68830,18 +68912,15 @@
         <v>5.820895522388058</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>354.0525525525526</v>
       </c>
       <c r="I13" t="n">
-        <v>354.0525525525526</v>
+        <v>3.513513513513513</v>
       </c>
       <c r="J13" t="n">
-        <v>3.513513513513513</v>
-      </c>
-      <c r="K13" t="n">
         <v>0.9923706207405458</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68874,18 +68953,15 @@
         <v>7.861271676300571</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>284.1246246246246</v>
       </c>
       <c r="I14" t="n">
-        <v>284.1246246246246</v>
+        <v>4.084084084084081</v>
       </c>
       <c r="J14" t="n">
-        <v>4.084084084084081</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.437427005659868</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68918,18 +68994,15 @@
         <v>8.851174934725835</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>339.0518018018018</v>
       </c>
       <c r="I15" t="n">
-        <v>339.0518018018018</v>
+        <v>5.090090090090082</v>
       </c>
       <c r="J15" t="n">
-        <v>5.090090090090082</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.50127209560313</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68962,18 +69035,15 @@
         <v>8.587443946188339</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>380.1456456456456</v>
       </c>
       <c r="I16" t="n">
-        <v>380.1456456456456</v>
+        <v>5.75075075075075</v>
       </c>
       <c r="J16" t="n">
-        <v>5.75075075075075</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.512775647076946</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69006,18 +69076,15 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>182.1201201201202</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>182.1201201201202</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69050,18 +69117,15 @@
         <v>6.57407407407407</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>183.0210210210211</v>
       </c>
       <c r="I18" t="n">
-        <v>183.0210210210211</v>
+        <v>2.13213213213213</v>
       </c>
       <c r="J18" t="n">
-        <v>2.13213213213213</v>
-      </c>
-      <c r="K18" t="n">
         <v>1.164965707347487</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69094,18 +69158,15 @@
         <v>7.222222222222229</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>183.6216216216217</v>
       </c>
       <c r="I19" t="n">
-        <v>183.6216216216217</v>
+        <v>2.342342342342344</v>
       </c>
       <c r="J19" t="n">
-        <v>2.342342342342344</v>
-      </c>
-      <c r="K19" t="n">
         <v>1.275635364537337</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69138,18 +69199,15 @@
         <v>8.006329113924055</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>268.8318318318318</v>
       </c>
       <c r="I20" t="n">
-        <v>268.8318318318318</v>
+        <v>3.7987987987988</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7987987987988</v>
-      </c>
-      <c r="K20" t="n">
         <v>1.413076261435865</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69182,18 +69240,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>341.4542042042042</v>
       </c>
       <c r="I21" t="n">
-        <v>341.4542042042042</v>
+        <v>5.750750750750743</v>
       </c>
       <c r="J21" t="n">
-        <v>5.750750750750743</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.684193862586489</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69226,18 +69281,15 @@
         <v>8.509933774834426</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>258.0315315315315</v>
       </c>
       <c r="I22" t="n">
-        <v>258.0315315315315</v>
+        <v>3.858858858858853</v>
       </c>
       <c r="J22" t="n">
-        <v>3.858858858858853</v>
-      </c>
-      <c r="K22" t="n">
         <v>1.495498955478354</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69270,18 +69322,15 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>218.1261261261261</v>
+      </c>
+      <c r="I23" t="n">
         <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>218.1261261261261</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69314,18 +69363,15 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>226.2342342342343</v>
+      </c>
+      <c r="I24" t="n">
         <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>226.2342342342343</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69358,18 +69404,15 @@
         <v>7.07509881422926</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>204.6148648648649</v>
       </c>
       <c r="I25" t="n">
-        <v>204.6148648648649</v>
+        <v>2.687687687687692</v>
       </c>
       <c r="J25" t="n">
-        <v>2.687687687687692</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.313534913244323</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69402,18 +69445,15 @@
         <v>7.222222222222229</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>204.6426426426426</v>
       </c>
       <c r="I26" t="n">
-        <v>204.6426426426426</v>
+        <v>2.342342342342344</v>
       </c>
       <c r="J26" t="n">
-        <v>2.342342342342344</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.144601297214805</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69446,18 +69486,15 @@
         <v>9.999999999999993</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>390.0555555555555</v>
       </c>
       <c r="I27" t="n">
-        <v>390.0555555555555</v>
+        <v>6.696696696696692</v>
       </c>
       <c r="J27" t="n">
-        <v>6.696696696696692</v>
-      </c>
-      <c r="K27" t="n">
         <v>1.716857150556052</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69490,18 +69527,15 @@
         <v>8.230337078651678</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>309.942942942943</v>
       </c>
       <c r="I28" t="n">
-        <v>309.942942942943</v>
+        <v>4.399399399399394</v>
       </c>
       <c r="J28" t="n">
-        <v>4.399399399399394</v>
-      </c>
-      <c r="K28" t="n">
         <v>1.419422348393095</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69534,18 +69568,15 @@
         <v>4.241573033707859</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>294.3273273273272</v>
       </c>
       <c r="I29" t="n">
-        <v>294.3273273273272</v>
+        <v>2.267267267267264</v>
       </c>
       <c r="J29" t="n">
-        <v>2.267267267267264</v>
-      </c>
-      <c r="K29" t="n">
         <v>0.770321698584852</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69578,18 +69609,15 @@
         <v>7.106741573033698</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>308.7417417417417</v>
       </c>
       <c r="I30" t="n">
-        <v>308.7417417417417</v>
+        <v>3.798798798798793</v>
       </c>
       <c r="J30" t="n">
-        <v>3.798798798798793</v>
-      </c>
-      <c r="K30" t="n">
         <v>1.230413088093685</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69622,18 +69650,15 @@
         <v>9.999999999999993</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>381.0465465465466</v>
       </c>
       <c r="I31" t="n">
-        <v>381.0465465465466</v>
+        <v>6.696696696696692</v>
       </c>
       <c r="J31" t="n">
-        <v>6.696696696696692</v>
-      </c>
-      <c r="K31" t="n">
         <v>1.757448468537337</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69666,18 +69691,15 @@
         <v>4.801324503311244</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>267.0405405405406</v>
       </c>
       <c r="I32" t="n">
-        <v>267.0405405405406</v>
+        <v>2.177177177177171</v>
       </c>
       <c r="J32" t="n">
-        <v>2.177177177177171</v>
-      </c>
-      <c r="K32" t="n">
         <v>0.8152983710900795</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69710,18 +69732,15 @@
         <v>7.861271676300571</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>299.1396396396397</v>
       </c>
       <c r="I33" t="n">
-        <v>299.1396396396397</v>
+        <v>4.084084084084081</v>
       </c>
       <c r="J33" t="n">
-        <v>4.084084084084081</v>
-      </c>
-      <c r="K33" t="n">
         <v>1.365276794811947</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69754,18 +69773,15 @@
         <v>8.006329113924055</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>259.5225225225225</v>
       </c>
       <c r="I34" t="n">
-        <v>259.5225225225225</v>
+        <v>3.7987987987988</v>
       </c>
       <c r="J34" t="n">
-        <v>3.7987987987988</v>
-      </c>
-      <c r="K34" t="n">
         <v>1.463764594253712</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69798,18 +69814,15 @@
         <v>6.83544303797469</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>287.4504504504504</v>
       </c>
       <c r="I35" t="n">
-        <v>287.4504504504504</v>
+        <v>3.243243243243246</v>
       </c>
       <c r="J35" t="n">
-        <v>3.243243243243246</v>
-      </c>
-      <c r="K35" t="n">
         <v>1.128279061021094</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69842,18 +69855,15 @@
         <v>6.416382252559718</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>258.0382882882883</v>
       </c>
       <c r="I36" t="n">
-        <v>258.0382882882883</v>
+        <v>2.822822822822818</v>
       </c>
       <c r="J36" t="n">
-        <v>2.822822822822818</v>
-      </c>
-      <c r="K36" t="n">
         <v>1.093955025646843</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69886,18 +69896,15 @@
         <v>7.86069651741292</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>351.6501501501502</v>
       </c>
       <c r="I37" t="n">
-        <v>351.6501501501502</v>
+        <v>4.744744744744735</v>
       </c>
       <c r="J37" t="n">
-        <v>4.744744744744735</v>
-      </c>
-      <c r="K37" t="n">
         <v>1.349279885908989</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69930,18 +69937,15 @@
         <v>8.53754940711463</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>236.1463963963963</v>
       </c>
       <c r="I38" t="n">
-        <v>236.1463963963963</v>
+        <v>3.243243243243246</v>
       </c>
       <c r="J38" t="n">
-        <v>3.243243243243246</v>
-      </c>
-      <c r="K38" t="n">
         <v>1.373403656687237</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69974,18 +69978,15 @@
         <v>9.999999999999984</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>327.960960960961</v>
       </c>
       <c r="I39" t="n">
-        <v>327.960960960961</v>
+        <v>5.345345345345336</v>
       </c>
       <c r="J39" t="n">
-        <v>5.345345345345336</v>
-      </c>
-      <c r="K39" t="n">
         <v>1.629872448746003</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70018,18 +70019,15 @@
         <v>6.57407407407407</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>185.4234234234234</v>
       </c>
       <c r="I40" t="n">
-        <v>185.4234234234234</v>
+        <v>2.13213213213213</v>
       </c>
       <c r="J40" t="n">
-        <v>2.13213213213213</v>
-      </c>
-      <c r="K40" t="n">
         <v>1.149872056489488</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70062,18 +70060,15 @@
         <v>6.57407407407407</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>190.5285285285286</v>
       </c>
       <c r="I41" t="n">
-        <v>190.5285285285286</v>
+        <v>2.13213213213213</v>
       </c>
       <c r="J41" t="n">
-        <v>2.13213213213213</v>
-      </c>
-      <c r="K41" t="n">
         <v>1.119061879393499</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70106,18 +70101,15 @@
         <v>8.634812286689408</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>266.1463963963964</v>
       </c>
       <c r="I42" t="n">
-        <v>266.1463963963964</v>
+        <v>3.798798798798793</v>
       </c>
       <c r="J42" t="n">
-        <v>3.798798798798793</v>
-      </c>
-      <c r="K42" t="n">
         <v>1.427334298053351</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70150,18 +70142,15 @@
         <v>1.225165562913905</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>257.1306306306306</v>
       </c>
       <c r="I43" t="n">
-        <v>257.1306306306306</v>
+        <v>0.5555555555555544</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5555555555555544</v>
-      </c>
-      <c r="K43" t="n">
         <v>0.2160596558228073</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70194,18 +70183,15 @@
         <v>7.372013651877124</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>276.0563063063063</v>
       </c>
       <c r="I44" t="n">
-        <v>276.0563063063063</v>
+        <v>3.243243243243239</v>
       </c>
       <c r="J44" t="n">
-        <v>3.243243243243239</v>
-      </c>
-      <c r="K44" t="n">
         <v>1.174848452708269</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70238,18 +70224,15 @@
         <v>9.999999999999991</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>355.2537537537538</v>
       </c>
       <c r="I45" t="n">
-        <v>355.2537537537538</v>
+        <v>6.036036036036031</v>
       </c>
       <c r="J45" t="n">
-        <v>6.036036036036031</v>
-      </c>
-      <c r="K45" t="n">
         <v>1.699077341831536</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70282,18 +70265,15 @@
         <v>8.93063583815028</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>292.5330330330331</v>
       </c>
       <c r="I46" t="n">
-        <v>292.5330330330331</v>
+        <v>4.639639639639635</v>
       </c>
       <c r="J46" t="n">
-        <v>4.639639639639635</v>
-      </c>
-      <c r="K46" t="n">
         <v>1.586022471218053</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70326,18 +70306,15 @@
         <v>5.927152317880774</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>254.1276276276276</v>
       </c>
       <c r="I47" t="n">
-        <v>254.1276276276276</v>
+        <v>2.687687687687678</v>
       </c>
       <c r="J47" t="n">
-        <v>2.687687687687678</v>
-      </c>
-      <c r="K47" t="n">
         <v>1.057613338926667</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70370,18 +70347,15 @@
         <v>10.00000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>201.3393393393393</v>
       </c>
       <c r="I48" t="n">
-        <v>201.3393393393393</v>
+        <v>3.243243243243246</v>
       </c>
       <c r="J48" t="n">
-        <v>3.243243243243246</v>
-      </c>
-      <c r="K48" t="n">
         <v>1.610834352534082</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70414,18 +70388,15 @@
         <v>6.791907514450862</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>288.6291291291291</v>
       </c>
       <c r="I49" t="n">
-        <v>288.6291291291291</v>
+        <v>3.528528528528526</v>
       </c>
       <c r="J49" t="n">
-        <v>3.528528528528526</v>
-      </c>
-      <c r="K49" t="n">
         <v>1.222512966440718</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70458,18 +70429,15 @@
         <v>7.690582959641254</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>384.9504504504504</v>
       </c>
       <c r="I50" t="n">
-        <v>384.9504504504504</v>
+        <v>5.150150150150149</v>
       </c>
       <c r="J50" t="n">
-        <v>5.150150150150149</v>
-      </c>
-      <c r="K50" t="n">
         <v>1.337873522195829</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70502,18 +70470,15 @@
         <v>7.474402730375422</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>249.6298798798799</v>
       </c>
       <c r="I51" t="n">
-        <v>249.6298798798799</v>
+        <v>3.288288288288286</v>
       </c>
       <c r="J51" t="n">
-        <v>3.288288288288286</v>
-      </c>
-      <c r="K51" t="n">
         <v>1.317265501177418</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70530,7 +70495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70556,20 +70521,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -70602,9 +70562,6 @@
       <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -70625,15 +70582,12 @@
         <v>7.080422734827013</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>278.1684384384384</v>
       </c>
       <c r="G3" t="n">
-        <v>278.1684384384384</v>
+        <v>3.49249249249249</v>
       </c>
       <c r="H3" t="n">
-        <v>3.49249249249249</v>
-      </c>
-      <c r="I3" t="n">
         <v>1.216723941717838</v>
       </c>
     </row>
@@ -70656,15 +70610,12 @@
         <v>2.453817275191485</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>59.77643101218357</v>
       </c>
       <c r="G4" t="n">
-        <v>59.77643101218357</v>
+        <v>1.566759255730334</v>
       </c>
       <c r="H4" t="n">
-        <v>1.566759255730334</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.416747943937489</v>
       </c>
     </row>
@@ -70687,17 +70638,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
+        <v>182.1201201201202</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>182.1201201201202</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -70718,15 +70666,12 @@
         <v>6.620278875713658</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>229.3896396396397</v>
       </c>
       <c r="G6" t="n">
-        <v>229.3896396396397</v>
+        <v>2.567567567567571</v>
       </c>
       <c r="H6" t="n">
-        <v>2.567567567567571</v>
-      </c>
-      <c r="I6" t="n">
         <v>1.138459867180023</v>
       </c>
     </row>
@@ -70749,15 +70694,12 @@
         <v>7.652349723943074</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>272.6028528528528</v>
       </c>
       <c r="G7" t="n">
-        <v>272.6028528528528</v>
+        <v>3.633633633633633</v>
       </c>
       <c r="H7" t="n">
-        <v>3.633633633633633</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.326158506694248</v>
       </c>
     </row>
@@ -70780,15 +70722,12 @@
         <v>8.53064549904458</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>321.639451951952</v>
       </c>
       <c r="G8" t="n">
-        <v>321.639451951952</v>
+        <v>4.47822822822822</v>
       </c>
       <c r="H8" t="n">
-        <v>4.47822822822822</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.428078123239842</v>
       </c>
     </row>
@@ -70811,15 +70750,12 @@
         <v>10.00000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>390.0555555555555</v>
       </c>
       <c r="G9" t="n">
-        <v>390.0555555555555</v>
+        <v>6.696696696696692</v>
       </c>
       <c r="H9" t="n">
-        <v>6.696696696696692</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.757448468537337</v>
       </c>
     </row>
